--- a/data/trans_orig/P44-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P44-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2012</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2012 (tasa de respuesta: 97,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35779</t>
+          <t>35533</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64250</t>
+          <t>64050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51003</t>
+          <t>50968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83092</t>
+          <t>83152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93432</t>
+          <t>94473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137207</t>
+          <t>137127</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>585950</t>
+          <t>586150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>614421</t>
+          <t>614667</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>929242</t>
+          <t>929182</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>961331</t>
+          <t>961366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1525327</t>
+          <t>1525407</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1569102</t>
+          <t>1568061</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36013</t>
+          <t>36764</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65349</t>
+          <t>67877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20162</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44785</t>
+          <t>43475</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61940</t>
+          <t>61766</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100330</t>
+          <t>100043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>371212</t>
+          <t>368684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400548</t>
+          <t>399797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>344265</t>
+          <t>345575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368888</t>
+          <t>369011</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>725281</t>
+          <t>725568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>763671</t>
+          <t>763845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25290</t>
+          <t>25258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20057</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18591</t>
+          <t>18793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>40651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79632</t>
+          <t>79664</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96308</t>
+          <t>96075</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42929</t>
+          <t>41975</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56416</t>
+          <t>55809</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128164</t>
+          <t>127257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149317</t>
+          <t>149115</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92904</t>
+          <t>94338</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136614</t>
+          <t>137296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88445</t>
+          <t>89318</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131781</t>
+          <t>131620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193727</t>
+          <t>192644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253523</t>
+          <t>253366</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1055069</t>
+          <t>1054387</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1098779</t>
+          <t>1097345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1332589</t>
+          <t>1332750</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1375925</t>
+          <t>1375052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2402530</t>
+          <t>2402687</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2462326</t>
+          <t>2463409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2016</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42432</t>
+          <t>43484</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68451</t>
+          <t>69668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50018</t>
+          <t>48855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83122</t>
+          <t>82998</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100172</t>
+          <t>99574</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142838</t>
+          <t>142055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>481175</t>
+          <t>479958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>507194</t>
+          <t>506142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>728490</t>
+          <t>728614</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>761594</t>
+          <t>762757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1218399</t>
+          <t>1219182</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1261065</t>
+          <t>1261663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63310</t>
+          <t>64060</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98864</t>
+          <t>98870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26328</t>
+          <t>25486</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51135</t>
+          <t>51976</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98114</t>
+          <t>96142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139668</t>
+          <t>137895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583625</t>
+          <t>583619</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>619179</t>
+          <t>618429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>606773</t>
+          <t>605932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>631580</t>
+          <t>632422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1200728</t>
+          <t>1202501</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1242282</t>
+          <t>1244254</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>40786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27053</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32853</t>
+          <t>32506</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58574</t>
+          <t>59625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121340</t>
+          <t>121625</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142415</t>
+          <t>143192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94659</t>
+          <t>96532</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112047</t>
+          <t>112674</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>225549</t>
+          <t>224498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251270</t>
+          <t>251617</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141606</t>
+          <t>141796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189442</t>
+          <t>192300</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98246</t>
+          <t>97926</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141118</t>
+          <t>142018</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>249669</t>
+          <t>251348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315051</t>
+          <t>314389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1205084</t>
+          <t>1202226</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1252920</t>
+          <t>1252730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1450113</t>
+          <t>1449213</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1492985</t>
+          <t>1493305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2670706</t>
+          <t>2671368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2736088</t>
+          <t>2734409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2023</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2023 (tasa de respuesta: 98,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126013</t>
+          <t>127653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158738</t>
+          <t>158508</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>154090</t>
+          <t>154958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>186636</t>
+          <t>188908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>287718</t>
+          <t>288871</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>336191</t>
+          <t>334072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244084</t>
+          <t>244314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276809</t>
+          <t>275169</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>453372</t>
+          <t>451100</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>485918</t>
+          <t>485050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>706640</t>
+          <t>708759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>755113</t>
+          <t>753960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>342689</t>
+          <t>343676</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>789756</t>
+          <t>778037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121810</t>
+          <t>125442</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>292207</t>
+          <t>291936</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>498957</t>
+          <t>512364</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1168903</t>
+          <t>1163381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>236099</t>
+          <t>247818</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>683166</t>
+          <t>682179</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>647896</t>
+          <t>648167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>818293</t>
+          <t>814661</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>797055</t>
+          <t>802577</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1467001</t>
+          <t>1453594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107994</t>
+          <t>108093</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142239</t>
+          <t>139115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75463</t>
+          <t>75517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96112</t>
+          <t>96720</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>188094</t>
+          <t>190620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>229858</t>
+          <t>229056</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135425</t>
+          <t>138549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>169670</t>
+          <t>169571</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125181</t>
+          <t>124573</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145830</t>
+          <t>145776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269099</t>
+          <t>269901</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>310863</t>
+          <t>308337</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>61,8%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>612371</t>
+          <t>608739</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1133268</t>
+          <t>1098584</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>324322</t>
+          <t>316452</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>551922</t>
+          <t>550079</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1028084</t>
+          <t>1020576</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1737384</t>
+          <t>1711635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>573074</t>
+          <t>607758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1093971</t>
+          <t>1097603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1249482</t>
+          <t>1251325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1477082</t>
+          <t>1484952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1770362</t>
+          <t>1796111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2479662</t>
+          <t>2487170</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P44-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35533</t>
+          <t>35657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64050</t>
+          <t>66033</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50968</t>
+          <t>51978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83152</t>
+          <t>84553</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +782,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>114446</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>92776</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>136559</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>8,21%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>114446</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>94473</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>137127</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>586150</t>
+          <t>584167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>614667</t>
+          <t>614543</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>929182</t>
+          <t>927781</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>961366</t>
+          <t>960356</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +895,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>91,65%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1548088</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1525975</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1569758</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>93,12%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>91,79%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>94,97%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1438</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1548088</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1525407</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1568061</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>93,12%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36764</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67877</t>
+          <t>65470</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>20981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43475</t>
+          <t>44717</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61766</t>
+          <t>62607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100043</t>
+          <t>99217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368684</t>
+          <t>371091</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399797</t>
+          <t>399568</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345575</t>
+          <t>344333</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369011</t>
+          <t>368069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>725568</t>
+          <t>726394</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>763845</t>
+          <t>763004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25258</t>
+          <t>24875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21011</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40651</t>
+          <t>39440</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79664</t>
+          <t>80047</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96075</t>
+          <t>96722</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41975</t>
+          <t>42118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55809</t>
+          <t>56158</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127257</t>
+          <t>128468</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149115</t>
+          <t>149676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,14%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94338</t>
+          <t>91257</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137296</t>
+          <t>137073</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89318</t>
+          <t>88565</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131620</t>
+          <t>129757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192644</t>
+          <t>191766</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253366</t>
+          <t>251543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1054387</t>
+          <t>1054610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1097345</t>
+          <t>1100426</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1332750</t>
+          <t>1334613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1375052</t>
+          <t>1375805</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2402687</t>
+          <t>2404510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2463409</t>
+          <t>2464287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43484</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69668</t>
+          <t>70414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48855</t>
+          <t>50389</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82998</t>
+          <t>82563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99574</t>
+          <t>98322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142055</t>
+          <t>142642</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>479958</t>
+          <t>479212</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>506142</t>
+          <t>506944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>728614</t>
+          <t>729049</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>762757</t>
+          <t>761223</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1219182</t>
+          <t>1218595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1261663</t>
+          <t>1262915</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64060</t>
+          <t>65306</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98870</t>
+          <t>98786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25486</t>
+          <t>26872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51976</t>
+          <t>51890</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96142</t>
+          <t>97593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137895</t>
+          <t>139317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583619</t>
+          <t>583703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>618429</t>
+          <t>617183</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>605932</t>
+          <t>606018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>632422</t>
+          <t>631036</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1202501</t>
+          <t>1201079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1244254</t>
+          <t>1242803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19219</t>
+          <t>19682</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40786</t>
+          <t>40699</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>26673</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32506</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59625</t>
+          <t>60063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121625</t>
+          <t>121712</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143192</t>
+          <t>142729</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96532</t>
+          <t>95039</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112674</t>
+          <t>112373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>224498</t>
+          <t>224060</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251617</t>
+          <t>251465</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141796</t>
+          <t>140187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192300</t>
+          <t>192560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97926</t>
+          <t>97510</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142018</t>
+          <t>143518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>251348</t>
+          <t>250355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>314389</t>
+          <t>318093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1202226</t>
+          <t>1201966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1252730</t>
+          <t>1254339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1449213</t>
+          <t>1447713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1493305</t>
+          <t>1493721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2671368</t>
+          <t>2667664</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2734409</t>
+          <t>2735402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>142282</t>
+          <t>151674</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>127653</t>
+          <t>135018</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158508</t>
+          <t>169168</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>170682</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>154958</t>
+          <t>172000</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>188908</t>
+          <t>204589</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>312964</t>
+          <t>339742</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>288871</t>
+          <t>315675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>334072</t>
+          <t>363499</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>260540</t>
+          <t>283237</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244314</t>
+          <t>265743</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275169</t>
+          <t>299893</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>469326</t>
+          <t>503238</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>451100</t>
+          <t>486716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>485050</t>
+          <t>519305</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>729867</t>
+          <t>786474</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>708759</t>
+          <t>762717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>753960</t>
+          <t>810541</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>402822</t>
+          <t>434911</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>402822</t>
+          <t>434911</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>402822</t>
+          <t>434911</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>640008</t>
+          <t>691305</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>640008</t>
+          <t>691305</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>640008</t>
+          <t>691305</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1042831</t>
+          <t>1126216</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1042831</t>
+          <t>1126216</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1042831</t>
+          <t>1126216</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>512398</t>
+          <t>291623</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>343676</t>
+          <t>266920</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>778037</t>
+          <t>317145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>223015</t>
+          <t>244815</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125442</t>
+          <t>225950</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>291936</t>
+          <t>265687</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>735413</t>
+          <t>536437</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>512364</t>
+          <t>504191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1163381</t>
+          <t>567902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>513457</t>
+          <t>566616</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>247818</t>
+          <t>541094</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>682179</t>
+          <t>591319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>717088</t>
+          <t>562537</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>648167</t>
+          <t>541665</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>814661</t>
+          <t>581402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1230545</t>
+          <t>1129153</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>802577</t>
+          <t>1097688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1453594</t>
+          <t>1161399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1025855</t>
+          <t>858239</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1025855</t>
+          <t>858239</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1025855</t>
+          <t>858239</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>940103</t>
+          <t>807352</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>940103</t>
+          <t>807352</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>940103</t>
+          <t>807352</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1965958</t>
+          <t>1665590</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1965958</t>
+          <t>1665590</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1965958</t>
+          <t>1665590</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>123905</t>
+          <t>130103</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108093</t>
+          <t>113685</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139115</t>
+          <t>145704</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>85727</t>
+          <t>97120</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75517</t>
+          <t>83422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96720</t>
+          <t>108275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>209632</t>
+          <t>227223</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>190620</t>
+          <t>207558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>229056</t>
+          <t>246204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>153759</t>
+          <t>166017</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138549</t>
+          <t>150416</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>169571</t>
+          <t>182435</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>135566</t>
+          <t>150947</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124573</t>
+          <t>139792</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145776</t>
+          <t>164645</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>289325</t>
+          <t>316964</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269901</t>
+          <t>297983</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>308337</t>
+          <t>336629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,86%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>277664</t>
+          <t>296120</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>277664</t>
+          <t>296120</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>277664</t>
+          <t>296120</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>221293</t>
+          <t>248067</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221293</t>
+          <t>248067</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>221293</t>
+          <t>248067</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>498957</t>
+          <t>544187</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>498957</t>
+          <t>544187</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>498957</t>
+          <t>544187</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>778586</t>
+          <t>573400</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>608739</t>
+          <t>532966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1098584</t>
+          <t>604194</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>316452</t>
+          <t>501477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>550079</t>
+          <t>558440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1258010</t>
+          <t>1103402</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1020576</t>
+          <t>1054982</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1711635</t>
+          <t>1146162</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>927756</t>
+          <t>1015869</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607758</t>
+          <t>985075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1097603</t>
+          <t>1056303</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1321981</t>
+          <t>1216722</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1251325</t>
+          <t>1188284</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1484952</t>
+          <t>1245247</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2249736</t>
+          <t>2232592</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1796111</t>
+          <t>2189832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2487170</t>
+          <t>2281012</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1706342</t>
+          <t>1589269</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1706342</t>
+          <t>1589269</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1706342</t>
+          <t>1589269</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1801404</t>
+          <t>1746724</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1801404</t>
+          <t>1746724</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1801404</t>
+          <t>1746724</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3507746</t>
+          <t>3335994</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3507746</t>
+          <t>3335994</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3507746</t>
+          <t>3335994</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
